--- a/eval/results/evaluation_metrics_new30.xlsx
+++ b/eval/results/evaluation_metrics_new30.xlsx
@@ -486,25 +486,25 @@
         <v>480</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3875</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2366863905325444</v>
+        <v>0.2424242424242424</v>
       </c>
       <c r="D2" t="n">
         <v>0.1951219512195122</v>
       </c>
       <c r="E2" t="n">
-        <v>0.213903743315508</v>
+        <v>0.2162162162162162</v>
       </c>
       <c r="F2" t="n">
         <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="H2" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I2" t="n">
         <v>165</v>
@@ -520,28 +520,28 @@
         <v>480</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4229166666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2413793103448276</v>
+        <v>0.2428571428571429</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1707317073170732</v>
+        <v>0.1658536585365854</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2</v>
+        <v>0.1971014492753623</v>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G3" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H3" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="I3" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -588,28 +588,28 @@
         <v>480</v>
       </c>
       <c r="B5" t="n">
-        <v>0.41875</v>
+        <v>0.4104166666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2196969696969697</v>
+        <v>0.2214285714285714</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1414634146341463</v>
+        <v>0.1512195121951219</v>
       </c>
       <c r="E5" t="n">
-        <v>0.172106824925816</v>
+        <v>0.1797101449275362</v>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="H5" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="I5" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -622,28 +622,28 @@
         <v>480</v>
       </c>
       <c r="B6" t="n">
-        <v>0.48125</v>
+        <v>0.4604166666666666</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2659574468085106</v>
+        <v>0.2452830188679245</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1219512195121951</v>
+        <v>0.1268292682926829</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1672240802675585</v>
+        <v>0.1672025723472669</v>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6" t="n">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="H6" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="I6" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -724,28 +724,28 @@
         <v>480</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4729166666666667</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1927710843373494</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05853658536585366</v>
+        <v>0.07804878048780488</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08664259927797835</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="H9" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="I9" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -758,28 +758,28 @@
         <v>480</v>
       </c>
       <c r="B10" t="n">
-        <v>0.45</v>
+        <v>0.4145833333333334</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2478632478632479</v>
+        <v>0.2397260273972603</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1414634146341463</v>
+        <v>0.1707317073170732</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1801242236024845</v>
+        <v>0.1994301994301994</v>
       </c>
       <c r="F10" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="H10" t="n">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="I10" t="n">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -858,25 +858,25 @@
         <v>480</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3875</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2366863905325444</v>
+        <v>0.2424242424242424</v>
       </c>
       <c r="D2" t="n">
         <v>0.1951219512195122</v>
       </c>
       <c r="E2" t="n">
-        <v>0.213903743315508</v>
+        <v>0.2162162162162162</v>
       </c>
       <c r="F2" t="n">
         <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="H2" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I2" t="n">
         <v>165</v>
@@ -892,28 +892,28 @@
         <v>480</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4229166666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2413793103448276</v>
+        <v>0.2428571428571429</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1707317073170732</v>
+        <v>0.1658536585365854</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2</v>
+        <v>0.1971014492753623</v>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G3" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H3" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="I3" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -960,28 +960,28 @@
         <v>480</v>
       </c>
       <c r="B5" t="n">
-        <v>0.41875</v>
+        <v>0.4104166666666667</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2196969696969697</v>
+        <v>0.2214285714285714</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1414634146341463</v>
+        <v>0.1512195121951219</v>
       </c>
       <c r="E5" t="n">
-        <v>0.172106824925816</v>
+        <v>0.1797101449275362</v>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="H5" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="I5" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -994,28 +994,28 @@
         <v>480</v>
       </c>
       <c r="B6" t="n">
-        <v>0.48125</v>
+        <v>0.4604166666666666</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2659574468085106</v>
+        <v>0.2452830188679245</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1219512195121951</v>
+        <v>0.1268292682926829</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1672240802675585</v>
+        <v>0.1672025723472669</v>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6" t="n">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="H6" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="I6" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1096,28 +1096,28 @@
         <v>480</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4729166666666667</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1927710843373494</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05853658536585366</v>
+        <v>0.07804878048780488</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08664259927797835</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="H9" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="I9" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1130,28 +1130,28 @@
         <v>480</v>
       </c>
       <c r="B10" t="n">
-        <v>0.45</v>
+        <v>0.4145833333333334</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2478632478632479</v>
+        <v>0.2397260273972603</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1414634146341463</v>
+        <v>0.1707317073170732</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1801242236024845</v>
+        <v>0.1994301994301994</v>
       </c>
       <c r="F10" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G10" t="n">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="H10" t="n">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="I10" t="n">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>

--- a/eval/results/evaluation_metrics_new30.xlsx
+++ b/eval/results/evaluation_metrics_new30.xlsx
@@ -486,28 +486,28 @@
         <v>480</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3958333333333333</v>
+        <v>0.7354166666666667</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2424242424242424</v>
+        <v>0.7473309608540926</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1951219512195122</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2162162162162162</v>
+        <v>0.7678244972577696</v>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>210</v>
       </c>
       <c r="G2" t="n">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="H2" t="n">
-        <v>125</v>
+        <v>71</v>
       </c>
       <c r="I2" t="n">
-        <v>165</v>
+        <v>56</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -520,28 +520,28 @@
         <v>480</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4229166666666667</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2428571428571429</v>
+        <v>0.8145161290322581</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1658536585365854</v>
+        <v>0.7593984962406015</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1971014492753623</v>
+        <v>0.7859922178988327</v>
       </c>
       <c r="F3" t="n">
-        <v>34</v>
+        <v>202</v>
       </c>
       <c r="G3" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H3" t="n">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="I3" t="n">
-        <v>171</v>
+        <v>64</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -554,28 +554,28 @@
         <v>480</v>
       </c>
       <c r="B4" t="n">
-        <v>0.84375</v>
+        <v>0.775</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8611111111111112</v>
+        <v>0.8558558558558559</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7560975609756098</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8051948051948052</v>
+        <v>0.7786885245901639</v>
       </c>
       <c r="F4" t="n">
-        <v>155</v>
+        <v>190</v>
       </c>
       <c r="G4" t="n">
-        <v>250</v>
+        <v>182</v>
       </c>
       <c r="H4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I4" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -588,28 +588,28 @@
         <v>480</v>
       </c>
       <c r="B5" t="n">
-        <v>0.4104166666666667</v>
+        <v>0.7958333333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2214285714285714</v>
+        <v>0.8307086614173228</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1512195121951219</v>
+        <v>0.793233082706767</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1797101449275362</v>
+        <v>0.8115384615384615</v>
       </c>
       <c r="F5" t="n">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="G5" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="H5" t="n">
-        <v>109</v>
+        <v>43</v>
       </c>
       <c r="I5" t="n">
-        <v>174</v>
+        <v>55</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -622,28 +622,28 @@
         <v>480</v>
       </c>
       <c r="B6" t="n">
-        <v>0.4604166666666666</v>
+        <v>0.75</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2452830188679245</v>
+        <v>0.8613861386138614</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1268292682926829</v>
+        <v>0.6541353383458647</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1672025723472669</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>174</v>
       </c>
       <c r="G6" t="n">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H6" t="n">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="I6" t="n">
-        <v>179</v>
+        <v>92</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -656,28 +656,28 @@
         <v>480</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4520833333333333</v>
+        <v>0.81875</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2583333333333334</v>
+        <v>0.8942731277533039</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1512195121951219</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1907692307692308</v>
+        <v>0.823529411764706</v>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>203</v>
       </c>
       <c r="G7" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H7" t="n">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="I7" t="n">
-        <v>174</v>
+        <v>63</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -690,28 +690,28 @@
         <v>480</v>
       </c>
       <c r="B8" t="n">
-        <v>0.4458333333333334</v>
+        <v>0.6854166666666667</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2347826086956522</v>
+        <v>0.7889447236180904</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1317073170731707</v>
+        <v>0.5902255639097744</v>
       </c>
       <c r="E8" t="n">
-        <v>0.16875</v>
+        <v>0.6752688172043011</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>157</v>
       </c>
       <c r="G8" t="n">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="H8" t="n">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="I8" t="n">
-        <v>178</v>
+        <v>109</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -724,28 +724,28 @@
         <v>480</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1927710843373494</v>
+        <v>0.8192771084337349</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07804878048780488</v>
+        <v>0.5112781954887218</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>136</v>
       </c>
       <c r="G9" t="n">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="H9" t="n">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="I9" t="n">
-        <v>189</v>
+        <v>130</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -758,28 +758,28 @@
         <v>480</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4145833333333334</v>
+        <v>0.7583333333333333</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2397260273972603</v>
+        <v>0.8</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1707317073170732</v>
+        <v>0.7518796992481203</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1994301994301994</v>
+        <v>0.7751937984496123</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>200</v>
       </c>
       <c r="G10" t="n">
         <v>164</v>
       </c>
       <c r="H10" t="n">
-        <v>111</v>
+        <v>50</v>
       </c>
       <c r="I10" t="n">
-        <v>170</v>
+        <v>66</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -858,28 +858,28 @@
         <v>480</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3958333333333333</v>
+        <v>0.7354166666666667</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2424242424242424</v>
+        <v>0.7473309608540926</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1951219512195122</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2162162162162162</v>
+        <v>0.7678244972577696</v>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>210</v>
       </c>
       <c r="G2" t="n">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="H2" t="n">
-        <v>125</v>
+        <v>71</v>
       </c>
       <c r="I2" t="n">
-        <v>165</v>
+        <v>56</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -892,28 +892,28 @@
         <v>480</v>
       </c>
       <c r="B3" t="n">
-        <v>0.4229166666666667</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2428571428571429</v>
+        <v>0.8145161290322581</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1658536585365854</v>
+        <v>0.7593984962406015</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1971014492753623</v>
+        <v>0.7859922178988327</v>
       </c>
       <c r="F3" t="n">
-        <v>34</v>
+        <v>202</v>
       </c>
       <c r="G3" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H3" t="n">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="I3" t="n">
-        <v>171</v>
+        <v>64</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -926,28 +926,28 @@
         <v>480</v>
       </c>
       <c r="B4" t="n">
-        <v>0.84375</v>
+        <v>0.775</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8611111111111112</v>
+        <v>0.8558558558558559</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7560975609756098</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8051948051948052</v>
+        <v>0.7786885245901639</v>
       </c>
       <c r="F4" t="n">
-        <v>155</v>
+        <v>190</v>
       </c>
       <c r="G4" t="n">
-        <v>250</v>
+        <v>182</v>
       </c>
       <c r="H4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I4" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -960,28 +960,28 @@
         <v>480</v>
       </c>
       <c r="B5" t="n">
-        <v>0.4104166666666667</v>
+        <v>0.7958333333333333</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2214285714285714</v>
+        <v>0.8307086614173228</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1512195121951219</v>
+        <v>0.793233082706767</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1797101449275362</v>
+        <v>0.8115384615384615</v>
       </c>
       <c r="F5" t="n">
-        <v>31</v>
+        <v>211</v>
       </c>
       <c r="G5" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="H5" t="n">
-        <v>109</v>
+        <v>43</v>
       </c>
       <c r="I5" t="n">
-        <v>174</v>
+        <v>55</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -994,28 +994,28 @@
         <v>480</v>
       </c>
       <c r="B6" t="n">
-        <v>0.4604166666666666</v>
+        <v>0.75</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2452830188679245</v>
+        <v>0.8613861386138614</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1268292682926829</v>
+        <v>0.6541353383458647</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1672025723472669</v>
+        <v>0.7435897435897436</v>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>174</v>
       </c>
       <c r="G6" t="n">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H6" t="n">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="I6" t="n">
-        <v>179</v>
+        <v>92</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1028,28 +1028,28 @@
         <v>480</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4520833333333333</v>
+        <v>0.81875</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2583333333333334</v>
+        <v>0.8942731277533039</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1512195121951219</v>
+        <v>0.7631578947368421</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1907692307692308</v>
+        <v>0.823529411764706</v>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>203</v>
       </c>
       <c r="G7" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H7" t="n">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="I7" t="n">
-        <v>174</v>
+        <v>63</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1062,28 +1062,28 @@
         <v>480</v>
       </c>
       <c r="B8" t="n">
-        <v>0.4458333333333334</v>
+        <v>0.6854166666666667</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2347826086956522</v>
+        <v>0.7889447236180904</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1317073170731707</v>
+        <v>0.5902255639097744</v>
       </c>
       <c r="E8" t="n">
-        <v>0.16875</v>
+        <v>0.6752688172043011</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>157</v>
       </c>
       <c r="G8" t="n">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="H8" t="n">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="I8" t="n">
-        <v>178</v>
+        <v>109</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1096,28 +1096,28 @@
         <v>480</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1927710843373494</v>
+        <v>0.8192771084337349</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07804878048780488</v>
+        <v>0.5112781954887218</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>136</v>
       </c>
       <c r="G9" t="n">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="H9" t="n">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="I9" t="n">
-        <v>189</v>
+        <v>130</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1130,28 +1130,28 @@
         <v>480</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4145833333333334</v>
+        <v>0.7583333333333333</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2397260273972603</v>
+        <v>0.8</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1707317073170732</v>
+        <v>0.7518796992481203</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1994301994301994</v>
+        <v>0.7751937984496123</v>
       </c>
       <c r="F10" t="n">
-        <v>35</v>
+        <v>200</v>
       </c>
       <c r="G10" t="n">
         <v>164</v>
       </c>
       <c r="H10" t="n">
-        <v>111</v>
+        <v>50</v>
       </c>
       <c r="I10" t="n">
-        <v>170</v>
+        <v>66</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
